--- a/artfynd/A 62696-2025 artfynd.xlsx
+++ b/artfynd/A 62696-2025 artfynd.xlsx
@@ -945,10 +945,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130887092</v>
+        <v>130887121</v>
       </c>
       <c r="B4" t="n">
-        <v>57864</v>
+        <v>79221</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -956,31 +956,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -988,10 +983,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>495933</v>
+        <v>495911</v>
       </c>
       <c r="R4" t="n">
-        <v>7016163</v>
+        <v>7016227</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1026,17 +1021,13 @@
           <t>2026-01-26</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en levande gran nära kant mot ungskog.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1057,12 +1048,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1080,7 +1071,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130887090</v>
+        <v>130887092</v>
       </c>
       <c r="B5" t="n">
         <v>57864</v>
@@ -1113,7 +1104,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1123,10 +1114,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>495983</v>
+        <v>495933</v>
       </c>
       <c r="R5" t="n">
-        <v>7016212</v>
+        <v>7016163</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1163,7 +1154,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Välsnidat bohål på ca 1,75 meters höjd i en döende gran. Bohålets diameter är 4,5 cm.</t>
+          <t>Ringhack, äldre, på en levande gran nära kant mot ungskog.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1215,10 +1206,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130887121</v>
+        <v>130887089</v>
       </c>
       <c r="B6" t="n">
-        <v>79221</v>
+        <v>57864</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1226,26 +1217,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1253,10 +1249,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>495911</v>
+        <v>496018</v>
       </c>
       <c r="R6" t="n">
-        <v>7016227</v>
+        <v>7016278</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1291,13 +1287,17 @@
           <t>2026-01-26</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, i riklig mängd längs flera meter på en granstam. Med tydliga spår av sav/kådaflöden. Granen med ringhack står intill en enklare körväg.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1341,7 +1341,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130887089</v>
+        <v>130887090</v>
       </c>
       <c r="B7" t="n">
         <v>57864</v>
@@ -1374,7 +1374,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1384,10 +1384,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>496018</v>
+        <v>495983</v>
       </c>
       <c r="R7" t="n">
-        <v>7016278</v>
+        <v>7016212</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, i riklig mängd längs flera meter på en granstam. Med tydliga spår av sav/kådaflöden. Granen med ringhack står intill en enklare körväg.</t>
+          <t>Välsnidat bohål på ca 1,75 meters höjd i en döende gran. Bohålets diameter är 4,5 cm.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1476,38 +1476,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130887108</v>
+        <v>130887094</v>
       </c>
       <c r="B8" t="n">
-        <v>97845</v>
+        <v>57864</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1515,10 +1519,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>495742</v>
+        <v>495901</v>
       </c>
       <c r="R8" t="n">
-        <v>7016070</v>
+        <v>7016223</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1553,19 +1557,43 @@
           <t>2026-01-26</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en levande något grövre gammal gran nära kant mot ungskog.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1583,42 +1611,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130887094</v>
+        <v>130887108</v>
       </c>
       <c r="B9" t="n">
-        <v>57864</v>
+        <v>97845</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1626,10 +1650,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>495901</v>
+        <v>495742</v>
       </c>
       <c r="R9" t="n">
-        <v>7016223</v>
+        <v>7016070</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1664,43 +1688,19 @@
           <t>2026-01-26</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en levande något grövre gammal gran nära kant mot ungskog.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1718,7 +1718,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130887133</v>
+        <v>130887126</v>
       </c>
       <c r="B10" t="n">
         <v>79221</v>
@@ -1756,10 +1756,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>496017</v>
+        <v>495942</v>
       </c>
       <c r="R10" t="n">
-        <v>7016363</v>
+        <v>7016269</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1844,10 +1844,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130887088</v>
+        <v>130887123</v>
       </c>
       <c r="B11" t="n">
-        <v>57864</v>
+        <v>79221</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1855,46 +1855,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Palleråsen Södra, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>495679</v>
+        <v>495877</v>
       </c>
       <c r="R11" t="n">
-        <v>7016071</v>
+        <v>7016242</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1929,17 +1920,13 @@
           <t>2026-01-26</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran intill en mindre väg.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1960,12 +1947,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1983,7 +1970,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130887126</v>
+        <v>130887133</v>
       </c>
       <c r="B12" t="n">
         <v>79221</v>
@@ -2021,10 +2008,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>495942</v>
+        <v>496017</v>
       </c>
       <c r="R12" t="n">
-        <v>7016269</v>
+        <v>7016363</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2109,7 +2096,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130887102</v>
+        <v>130887100</v>
       </c>
       <c r="B13" t="n">
         <v>57864</v>
@@ -2142,7 +2129,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2152,10 +2139,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>495951</v>
+        <v>495805</v>
       </c>
       <c r="R13" t="n">
-        <v>7016339</v>
+        <v>7016271</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2192,14 +2179,14 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Gammalt bohål på 2 meters höjd i en stående död gran. Bohålet är 5 cm i diameter längst ut och ca 4 cm i diameter en bit in i ingångshålet. Ev. skapat av tretåig hackspett. Stående död ved som indikerar högt livsmiljövärde för tretåig hackspett finns på/kring fyndplatsen.</t>
+          <t>Ringhack, äldre, på en levande gran vid kanten mot ungskog. Spår av sav/kådaflöde på granens stam.</t>
         </is>
       </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="b">
         <v>0</v>
@@ -2244,7 +2231,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130887100</v>
+        <v>130887088</v>
       </c>
       <c r="B14" t="n">
         <v>57864</v>
@@ -2277,20 +2264,24 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Palleråsen Södra, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>495805</v>
+        <v>495679</v>
       </c>
       <c r="R14" t="n">
-        <v>7016271</v>
+        <v>7016071</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2327,7 +2318,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en levande gran vid kanten mot ungskog. Spår av sav/kådaflöde på granens stam.</t>
+          <t>Ringhack, färska, på en gran intill en mindre väg.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2379,10 +2370,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130887123</v>
+        <v>130887102</v>
       </c>
       <c r="B15" t="n">
-        <v>79221</v>
+        <v>57864</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2390,26 +2381,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2417,10 +2413,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>495877</v>
+        <v>495951</v>
       </c>
       <c r="R15" t="n">
-        <v>7016242</v>
+        <v>7016339</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2455,13 +2451,17 @@
           <t>2026-01-26</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Gammalt bohål på 2 meters höjd i en stående död gran. Bohålet är 5 cm i diameter längst ut och ca 4 cm i diameter en bit in i ingångshålet. Ev. skapat av tretåig hackspett. Stående död ved som indikerar högt livsmiljövärde för tretåig hackspett finns på/kring fyndplatsen.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF15" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2482,12 +2482,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2505,10 +2505,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130887125</v>
+        <v>130887095</v>
       </c>
       <c r="B16" t="n">
-        <v>79221</v>
+        <v>57864</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2516,26 +2516,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2543,10 +2548,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>495945</v>
+        <v>495890</v>
       </c>
       <c r="R16" t="n">
-        <v>7016232</v>
+        <v>7016236</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2581,13 +2586,17 @@
           <t>2026-01-26</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, enstaka högt upp på stammen av en levande gran nära kant mot ungskog.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2608,12 +2617,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2631,10 +2640,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130887095</v>
+        <v>130887125</v>
       </c>
       <c r="B17" t="n">
-        <v>57864</v>
+        <v>79221</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2642,31 +2651,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2674,10 +2678,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>495890</v>
+        <v>495945</v>
       </c>
       <c r="R17" t="n">
-        <v>7016236</v>
+        <v>7016232</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2712,17 +2716,13 @@
           <t>2026-01-26</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, enstaka högt upp på stammen av en levande gran nära kant mot ungskog.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2743,12 +2743,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2766,10 +2766,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130887122</v>
+        <v>130887085</v>
       </c>
       <c r="B18" t="n">
-        <v>79221</v>
+        <v>57864</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2777,26 +2777,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2804,10 +2809,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>495898</v>
+        <v>495713</v>
       </c>
       <c r="R18" t="n">
-        <v>7016234</v>
+        <v>7015939</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2842,13 +2847,17 @@
           <t>2026-01-26</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, längs flera meter på en gran med spår efter påtagligt sav/kådaflöde.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2869,12 +2878,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2892,10 +2901,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130887085</v>
+        <v>130887122</v>
       </c>
       <c r="B19" t="n">
-        <v>57864</v>
+        <v>79221</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2903,31 +2912,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2935,10 +2939,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>495713</v>
+        <v>495898</v>
       </c>
       <c r="R19" t="n">
-        <v>7015939</v>
+        <v>7016234</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2973,17 +2977,13 @@
           <t>2026-01-26</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, längs flera meter på en gran med spår efter påtagligt sav/kådaflöde.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3027,37 +3027,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130887119</v>
+        <v>130887104</v>
       </c>
       <c r="B20" t="n">
-        <v>79221</v>
+        <v>80355</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -3065,10 +3073,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>495992</v>
+        <v>495828</v>
       </c>
       <c r="R20" t="n">
-        <v>7016329</v>
+        <v>7015949</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3105,7 +3113,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flera granar. Längsta bålen ca 80 cm.</t>
+          <t>Bålar av stuplav som täcker ca 3 dm2 sälg.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3120,27 +3128,27 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3158,40 +3166,39 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130887098</v>
+        <v>130887106</v>
       </c>
       <c r="B21" t="n">
-        <v>57864</v>
+        <v>80355</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -3201,10 +3208,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>495849</v>
+        <v>495981</v>
       </c>
       <c r="R21" t="n">
-        <v>7016251</v>
+        <v>7016252</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3241,7 +3248,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs några meter på en levande gran nära kant mot ungskog.</t>
+          <t>Enstaka bålar på en sälg.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3250,6 +3257,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3260,22 +3268,22 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3293,41 +3301,37 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130887106</v>
+        <v>130887119</v>
       </c>
       <c r="B22" t="n">
-        <v>80355</v>
+        <v>79221</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3335,10 +3339,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>495981</v>
+        <v>495992</v>
       </c>
       <c r="R22" t="n">
-        <v>7016252</v>
+        <v>7016329</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3375,7 +3379,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Enstaka bålar på en sälg.</t>
+          <t>Långväxta bålar på flera granar. Längsta bålen ca 80 cm.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3395,22 +3399,22 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3428,45 +3432,37 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130887104</v>
+        <v>130887116</v>
       </c>
       <c r="B23" t="n">
-        <v>80355</v>
+        <v>79221</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3474,10 +3470,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>495828</v>
+        <v>495725</v>
       </c>
       <c r="R23" t="n">
-        <v>7015949</v>
+        <v>7016183</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3514,7 +3510,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Bålar av stuplav som täcker ca 3 dm2 sälg.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3529,27 +3525,27 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3567,10 +3563,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130887116</v>
+        <v>130887098</v>
       </c>
       <c r="B24" t="n">
-        <v>79221</v>
+        <v>57864</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3578,26 +3574,31 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3605,10 +3606,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>495725</v>
+        <v>495849</v>
       </c>
       <c r="R24" t="n">
-        <v>7016183</v>
+        <v>7016251</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3645,7 +3646,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Ringhack, äldre, längs några meter på en levande gran nära kant mot ungskog.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3654,7 +3655,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3675,12 +3675,12 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3698,10 +3698,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130887120</v>
+        <v>130887107</v>
       </c>
       <c r="B25" t="n">
-        <v>79221</v>
+        <v>57861</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3709,41 +3709,50 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Palleråsen Södra, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>495991</v>
+        <v>495982</v>
       </c>
       <c r="R25" t="n">
-        <v>7016264</v>
+        <v>7016398</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3780,7 +3789,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Långväxta fertila bålar med apothecier.</t>
+          <t>1 eller möjligen 2 individer som sågs och hördes hacka i stående döda granar och uttryckte lockläte emellanåt. Hyfsat gott om stående död ved på/kring fyndplatsen.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3789,7 +3798,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3798,24 +3806,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Äldre bitvis flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3833,10 +3826,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130887107</v>
+        <v>130887120</v>
       </c>
       <c r="B26" t="n">
-        <v>57861</v>
+        <v>79221</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3844,50 +3837,41 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Palleråsen Södra, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>495982</v>
+        <v>495991</v>
       </c>
       <c r="R26" t="n">
-        <v>7016398</v>
+        <v>7016264</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3924,7 +3908,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>1 eller möjligen 2 individer som sågs och hördes hacka i stående döda granar och uttryckte lockläte emellanåt. Hyfsat gott om stående död ved på/kring fyndplatsen.</t>
+          <t>Långväxta fertila bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3933,6 +3917,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3941,9 +3926,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>Äldre bitvis flerskiktad granskog.</t>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4358,10 +4358,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130887132</v>
+        <v>130887086</v>
       </c>
       <c r="B30" t="n">
-        <v>79221</v>
+        <v>57864</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4369,26 +4369,31 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4396,10 +4401,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>496008</v>
+        <v>495683</v>
       </c>
       <c r="R30" t="n">
-        <v>7016340</v>
+        <v>7016064</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4436,7 +4441,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran. Ca 50 cm lång hängande bål.</t>
+          <t>Ringhack, färska, på en gran nära en mindre väg.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4445,7 +4450,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4466,12 +4470,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4489,10 +4493,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130887086</v>
+        <v>130887132</v>
       </c>
       <c r="B31" t="n">
-        <v>57864</v>
+        <v>79221</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4500,31 +4504,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4532,10 +4531,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>495683</v>
+        <v>496008</v>
       </c>
       <c r="R31" t="n">
-        <v>7016064</v>
+        <v>7016340</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4572,7 +4571,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran nära en mindre väg.</t>
+          <t>Långväxta bålar på gran. Ca 50 cm lång hängande bål.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4581,6 +4580,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4601,12 +4601,12 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -5282,7 +5282,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130887099</v>
+        <v>130887084</v>
       </c>
       <c r="B37" t="n">
         <v>57864</v>
@@ -5315,20 +5315,24 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Palleråsen Södra, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>495812</v>
+        <v>495868</v>
       </c>
       <c r="R37" t="n">
-        <v>7016273</v>
+        <v>7015959</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5365,7 +5369,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en levande gran nära kant mot ungskog.</t>
+          <t>Ringhack, färska, enstaka några meter upp på en granstam vid en glänta.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5417,7 +5421,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130887084</v>
+        <v>130887099</v>
       </c>
       <c r="B38" t="n">
         <v>57864</v>
@@ -5450,24 +5454,20 @@
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Palleråsen Södra, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>495868</v>
+        <v>495812</v>
       </c>
       <c r="R38" t="n">
-        <v>7015959</v>
+        <v>7016273</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5504,7 +5504,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack, färska, enstaka några meter upp på en granstam vid en glänta.</t>
+          <t>Ringhack, äldre, på en levande gran nära kant mot ungskog.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -6176,10 +6176,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130887129</v>
+        <v>130887087</v>
       </c>
       <c r="B44" t="n">
-        <v>79221</v>
+        <v>57864</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6187,26 +6187,31 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -6214,10 +6219,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>495878</v>
+        <v>495680</v>
       </c>
       <c r="R44" t="n">
-        <v>7016320</v>
+        <v>7016064</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6252,13 +6257,17 @@
           <t>2026-01-26</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en högväxt gran intill en mindre väg.</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -6279,12 +6288,12 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6302,10 +6311,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130887124</v>
+        <v>130887097</v>
       </c>
       <c r="B45" t="n">
-        <v>79221</v>
+        <v>57864</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6313,26 +6322,31 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -6340,10 +6354,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>495877</v>
+        <v>495856</v>
       </c>
       <c r="R45" t="n">
-        <v>7016270</v>
+        <v>7016255</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6380,7 +6394,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Ringhack, äldre, längs flera meter långt upp på en levande gran nära kant mot ungskog. Tydliga spår av sav/kådaflöde på granens stam.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6389,7 +6403,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -6410,12 +6423,12 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6433,10 +6446,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130887081</v>
+        <v>130887091</v>
       </c>
       <c r="B46" t="n">
-        <v>91776</v>
+        <v>57864</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6444,28 +6457,29 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
@@ -6475,10 +6489,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>495919</v>
+        <v>495967</v>
       </c>
       <c r="R46" t="n">
-        <v>7016205</v>
+        <v>7016170</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6515,7 +6529,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>I upplyft granlåga.</t>
+          <t>Ringhack, färska, på en levande gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6524,7 +6538,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -6545,12 +6558,12 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6568,10 +6581,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130887087</v>
+        <v>130887081</v>
       </c>
       <c r="B47" t="n">
-        <v>57864</v>
+        <v>91776</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6579,29 +6592,28 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
@@ -6611,10 +6623,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>495680</v>
+        <v>495919</v>
       </c>
       <c r="R47" t="n">
-        <v>7016064</v>
+        <v>7016205</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6651,7 +6663,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en högväxt gran intill en mindre väg.</t>
+          <t>I upplyft granlåga.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6660,6 +6672,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6680,12 +6693,12 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6703,10 +6716,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130887091</v>
+        <v>130887124</v>
       </c>
       <c r="B48" t="n">
-        <v>57864</v>
+        <v>79221</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6714,31 +6727,26 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6746,10 +6754,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>495967</v>
+        <v>495877</v>
       </c>
       <c r="R48" t="n">
-        <v>7016170</v>
+        <v>7016270</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6786,7 +6794,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en levande gran vid en hyggeskant.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6795,6 +6803,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6815,12 +6824,12 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6838,10 +6847,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130887097</v>
+        <v>130887129</v>
       </c>
       <c r="B49" t="n">
-        <v>57864</v>
+        <v>79221</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6849,31 +6858,26 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6881,10 +6885,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>495856</v>
+        <v>495878</v>
       </c>
       <c r="R49" t="n">
-        <v>7016255</v>
+        <v>7016320</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6919,17 +6923,13 @@
           <t>2026-01-26</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, längs flera meter långt upp på en levande gran nära kant mot ungskog. Tydliga spår av sav/kådaflöde på granens stam.</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6950,12 +6950,12 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6973,10 +6973,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130887101</v>
+        <v>130887112</v>
       </c>
       <c r="B50" t="n">
-        <v>57864</v>
+        <v>79221</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6984,46 +6984,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Palleråsen Södra, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>495852</v>
+        <v>495735</v>
       </c>
       <c r="R50" t="n">
-        <v>7016315</v>
+        <v>7016071</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -7060,7 +7051,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack, färska, längs ca 3 meter på en levande gran vid en lucka i skogen. En volym av stående död ved av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett på fyndplatsen.</t>
+          <t>Enstaka bålar på gran.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7069,6 +7060,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -7077,11 +7069,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI50" t="inlineStr">
-        <is>
-          <t>Äldre bitvis flerskiktad granskog med inslag av tall, björk, sälg och gråal.</t>
-        </is>
-      </c>
       <c r="AJ50" t="inlineStr">
         <is>
           <t>gran</t>
@@ -7094,12 +7081,12 @@
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7117,10 +7104,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130887112</v>
+        <v>130887101</v>
       </c>
       <c r="B51" t="n">
-        <v>79221</v>
+        <v>57864</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7128,37 +7115,46 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Palleråsen Södra, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>495735</v>
+        <v>495852</v>
       </c>
       <c r="R51" t="n">
-        <v>7016071</v>
+        <v>7016315</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7195,7 +7191,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Enstaka bålar på gran.</t>
+          <t>Ringhack, färska, längs ca 3 meter på en levande gran vid en lucka i skogen. En volym av stående död ved av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett på fyndplatsen.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7204,7 +7200,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -7213,6 +7208,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>Äldre bitvis flerskiktad granskog med inslag av tall, björk, sälg och gråal.</t>
+        </is>
+      </c>
       <c r="AJ51" t="inlineStr">
         <is>
           <t>gran</t>
@@ -7225,12 +7225,12 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>

--- a/artfynd/A 62696-2025 artfynd.xlsx
+++ b/artfynd/A 62696-2025 artfynd.xlsx
@@ -814,10 +814,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130887118</v>
+        <v>130887092</v>
       </c>
       <c r="B3" t="n">
-        <v>79221</v>
+        <v>57864</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -825,26 +825,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -852,10 +857,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>495992</v>
+        <v>495933</v>
       </c>
       <c r="R3" t="n">
-        <v>7016301</v>
+        <v>7016163</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,7 +897,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På gran intill andra hänglavar.</t>
+          <t>Ringhack, äldre, på en levande gran nära kant mot ungskog.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,7 +906,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -922,12 +926,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -945,10 +949,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130887121</v>
+        <v>130887089</v>
       </c>
       <c r="B4" t="n">
-        <v>79221</v>
+        <v>57864</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -956,26 +960,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -983,10 +992,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>495911</v>
+        <v>496018</v>
       </c>
       <c r="R4" t="n">
-        <v>7016227</v>
+        <v>7016278</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1021,13 +1030,17 @@
           <t>2026-01-26</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, i riklig mängd längs flera meter på en granstam. Med tydliga spår av sav/kådaflöden. Granen med ringhack står intill en enklare körväg.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1048,12 +1061,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1071,7 +1084,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130887092</v>
+        <v>130887090</v>
       </c>
       <c r="B5" t="n">
         <v>57864</v>
@@ -1104,7 +1117,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1114,10 +1127,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>495933</v>
+        <v>495983</v>
       </c>
       <c r="R5" t="n">
-        <v>7016163</v>
+        <v>7016212</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1154,7 +1167,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en levande gran nära kant mot ungskog.</t>
+          <t>Välsnidat bohål på ca 1,75 meters höjd i en döende gran. Bohålets diameter är 4,5 cm.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1206,10 +1219,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130887089</v>
+        <v>130887118</v>
       </c>
       <c r="B6" t="n">
-        <v>57864</v>
+        <v>79221</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,31 +1230,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1249,10 +1257,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>496018</v>
+        <v>495992</v>
       </c>
       <c r="R6" t="n">
-        <v>7016278</v>
+        <v>7016301</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1289,7 +1297,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, i riklig mängd längs flera meter på en granstam. Med tydliga spår av sav/kådaflöden. Granen med ringhack står intill en enklare körväg.</t>
+          <t>På gran intill andra hänglavar.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1298,6 +1306,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1318,12 +1327,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1341,10 +1350,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130887090</v>
+        <v>130887121</v>
       </c>
       <c r="B7" t="n">
-        <v>57864</v>
+        <v>79221</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1352,31 +1361,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1384,10 +1388,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>495983</v>
+        <v>495911</v>
       </c>
       <c r="R7" t="n">
-        <v>7016212</v>
+        <v>7016227</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1422,17 +1426,13 @@
           <t>2026-01-26</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Välsnidat bohål på ca 1,75 meters höjd i en döende gran. Bohålets diameter är 4,5 cm.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1453,12 +1453,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1476,42 +1476,38 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130887094</v>
+        <v>130887108</v>
       </c>
       <c r="B8" t="n">
-        <v>57864</v>
+        <v>97845</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1519,10 +1515,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>495901</v>
+        <v>495742</v>
       </c>
       <c r="R8" t="n">
-        <v>7016223</v>
+        <v>7016070</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1557,43 +1553,19 @@
           <t>2026-01-26</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en levande något grövre gammal gran nära kant mot ungskog.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1611,38 +1583,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130887108</v>
+        <v>130887094</v>
       </c>
       <c r="B9" t="n">
-        <v>97845</v>
+        <v>57864</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1650,10 +1626,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>495742</v>
+        <v>495901</v>
       </c>
       <c r="R9" t="n">
-        <v>7016070</v>
+        <v>7016223</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1688,19 +1664,43 @@
           <t>2026-01-26</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en levande något grövre gammal gran nära kant mot ungskog.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -2505,10 +2505,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130887095</v>
+        <v>130887125</v>
       </c>
       <c r="B16" t="n">
-        <v>57864</v>
+        <v>79221</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2516,31 +2516,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2548,10 +2543,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>495890</v>
+        <v>495945</v>
       </c>
       <c r="R16" t="n">
-        <v>7016236</v>
+        <v>7016232</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2586,17 +2581,13 @@
           <t>2026-01-26</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, enstaka högt upp på stammen av en levande gran nära kant mot ungskog.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2617,12 +2608,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2640,10 +2631,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130887125</v>
+        <v>130887095</v>
       </c>
       <c r="B17" t="n">
-        <v>79221</v>
+        <v>57864</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2651,26 +2642,31 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2678,10 +2674,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>495945</v>
+        <v>495890</v>
       </c>
       <c r="R17" t="n">
-        <v>7016232</v>
+        <v>7016236</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2716,13 +2712,17 @@
           <t>2026-01-26</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, enstaka högt upp på stammen av en levande gran nära kant mot ungskog.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2743,12 +2743,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -4223,10 +4223,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130887096</v>
+        <v>130887132</v>
       </c>
       <c r="B29" t="n">
-        <v>57864</v>
+        <v>79221</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4234,31 +4234,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -4266,10 +4261,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>495870</v>
+        <v>496008</v>
       </c>
       <c r="R29" t="n">
-        <v>7016247</v>
+        <v>7016340</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4306,7 +4301,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en levande gran nära kant mot ungskog.</t>
+          <t>Långväxta bålar på gran. Ca 50 cm lång hängande bål.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4315,6 +4310,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4335,12 +4331,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4358,10 +4354,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130887086</v>
+        <v>130887127</v>
       </c>
       <c r="B30" t="n">
-        <v>57864</v>
+        <v>79221</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4369,31 +4365,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4401,10 +4392,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>495683</v>
+        <v>495831</v>
       </c>
       <c r="R30" t="n">
-        <v>7016064</v>
+        <v>7016258</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4441,7 +4432,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran nära en mindre väg.</t>
+          <t>På en gren av gran på ca 2 m höjd.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4450,6 +4441,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4470,12 +4462,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4493,10 +4485,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130887132</v>
+        <v>130887096</v>
       </c>
       <c r="B31" t="n">
-        <v>79221</v>
+        <v>57864</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4504,26 +4496,31 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4531,10 +4528,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>496008</v>
+        <v>495870</v>
       </c>
       <c r="R31" t="n">
-        <v>7016340</v>
+        <v>7016247</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4571,7 +4568,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran. Ca 50 cm lång hängande bål.</t>
+          <t>Ringhack, äldre, på en levande gran nära kant mot ungskog.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4580,7 +4577,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4601,12 +4597,12 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4624,10 +4620,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130887127</v>
+        <v>130887086</v>
       </c>
       <c r="B32" t="n">
-        <v>79221</v>
+        <v>57864</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4635,26 +4631,31 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4662,10 +4663,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>495831</v>
+        <v>495683</v>
       </c>
       <c r="R32" t="n">
-        <v>7016258</v>
+        <v>7016064</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4702,7 +4703,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På en gren av gran på ca 2 m höjd.</t>
+          <t>Ringhack, färska, på en gran nära en mindre väg.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4711,7 +4712,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4732,12 +4732,12 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -5920,41 +5920,37 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130887105</v>
+        <v>130887114</v>
       </c>
       <c r="B42" t="n">
-        <v>80355</v>
+        <v>79221</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5962,10 +5958,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>495736</v>
+        <v>495689</v>
       </c>
       <c r="R42" t="n">
-        <v>7016168</v>
+        <v>7015994</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -6017,22 +6013,22 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6050,37 +6046,41 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130887114</v>
+        <v>130887105</v>
       </c>
       <c r="B43" t="n">
-        <v>79221</v>
+        <v>80355</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -6088,10 +6088,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>495689</v>
+        <v>495736</v>
       </c>
       <c r="R43" t="n">
-        <v>7015994</v>
+        <v>7016168</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6143,22 +6143,22 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6176,10 +6176,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130887087</v>
+        <v>130887124</v>
       </c>
       <c r="B44" t="n">
-        <v>57864</v>
+        <v>79221</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6187,31 +6187,26 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -6219,10 +6214,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>495680</v>
+        <v>495877</v>
       </c>
       <c r="R44" t="n">
-        <v>7016064</v>
+        <v>7016270</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6259,7 +6254,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en högväxt gran intill en mindre väg.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6268,6 +6263,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -6288,12 +6284,12 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6311,10 +6307,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130887097</v>
+        <v>130887129</v>
       </c>
       <c r="B45" t="n">
-        <v>57864</v>
+        <v>79221</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6322,31 +6318,26 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -6354,10 +6345,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>495856</v>
+        <v>495878</v>
       </c>
       <c r="R45" t="n">
-        <v>7016255</v>
+        <v>7016320</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6392,17 +6383,13 @@
           <t>2026-01-26</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, längs flera meter långt upp på en levande gran nära kant mot ungskog. Tydliga spår av sav/kådaflöde på granens stam.</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -6423,12 +6410,12 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6446,10 +6433,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130887091</v>
+        <v>130887081</v>
       </c>
       <c r="B46" t="n">
-        <v>57864</v>
+        <v>91776</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6457,29 +6444,28 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
@@ -6489,10 +6475,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>495967</v>
+        <v>495919</v>
       </c>
       <c r="R46" t="n">
-        <v>7016170</v>
+        <v>7016205</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6529,7 +6515,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en levande gran vid en hyggeskant.</t>
+          <t>I upplyft granlåga.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6538,6 +6524,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -6558,12 +6545,12 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6581,10 +6568,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130887081</v>
+        <v>130887087</v>
       </c>
       <c r="B47" t="n">
-        <v>91776</v>
+        <v>57864</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6592,28 +6579,29 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
@@ -6623,10 +6611,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>495919</v>
+        <v>495680</v>
       </c>
       <c r="R47" t="n">
-        <v>7016205</v>
+        <v>7016064</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6663,7 +6651,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>I upplyft granlåga.</t>
+          <t>Ringhack, färska, på en högväxt gran intill en mindre väg.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6672,7 +6660,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6693,12 +6680,12 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6716,10 +6703,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130887124</v>
+        <v>130887097</v>
       </c>
       <c r="B48" t="n">
-        <v>79221</v>
+        <v>57864</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6727,26 +6714,31 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6754,10 +6746,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>495877</v>
+        <v>495856</v>
       </c>
       <c r="R48" t="n">
-        <v>7016270</v>
+        <v>7016255</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6794,7 +6786,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Ringhack, äldre, längs flera meter långt upp på en levande gran nära kant mot ungskog. Tydliga spår av sav/kådaflöde på granens stam.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6803,7 +6795,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6824,12 +6815,12 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6847,10 +6838,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130887129</v>
+        <v>130887091</v>
       </c>
       <c r="B49" t="n">
-        <v>79221</v>
+        <v>57864</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6858,26 +6849,31 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6885,10 +6881,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>495878</v>
+        <v>495967</v>
       </c>
       <c r="R49" t="n">
-        <v>7016320</v>
+        <v>7016170</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6923,13 +6919,17 @@
           <t>2026-01-26</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en levande gran vid en hyggeskant.</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6950,12 +6950,12 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>

--- a/artfynd/A 62696-2025 artfynd.xlsx
+++ b/artfynd/A 62696-2025 artfynd.xlsx
@@ -814,10 +814,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130887092</v>
+        <v>130887118</v>
       </c>
       <c r="B3" t="n">
-        <v>57864</v>
+        <v>79221</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -825,31 +825,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -857,10 +852,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>495933</v>
+        <v>495992</v>
       </c>
       <c r="R3" t="n">
-        <v>7016163</v>
+        <v>7016301</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,7 +892,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en levande gran nära kant mot ungskog.</t>
+          <t>På gran intill andra hänglavar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,6 +901,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -926,12 +922,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -949,10 +945,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130887089</v>
+        <v>130887121</v>
       </c>
       <c r="B4" t="n">
-        <v>57864</v>
+        <v>79221</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -960,31 +956,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -992,10 +983,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>496018</v>
+        <v>495911</v>
       </c>
       <c r="R4" t="n">
-        <v>7016278</v>
+        <v>7016227</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1030,17 +1021,13 @@
           <t>2026-01-26</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, i riklig mängd längs flera meter på en granstam. Med tydliga spår av sav/kådaflöden. Granen med ringhack står intill en enklare körväg.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1061,12 +1048,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1084,7 +1071,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130887090</v>
+        <v>130887092</v>
       </c>
       <c r="B5" t="n">
         <v>57864</v>
@@ -1117,7 +1104,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1127,10 +1114,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>495983</v>
+        <v>495933</v>
       </c>
       <c r="R5" t="n">
-        <v>7016212</v>
+        <v>7016163</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1167,7 +1154,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Välsnidat bohål på ca 1,75 meters höjd i en döende gran. Bohålets diameter är 4,5 cm.</t>
+          <t>Ringhack, äldre, på en levande gran nära kant mot ungskog.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1219,10 +1206,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130887118</v>
+        <v>130887089</v>
       </c>
       <c r="B6" t="n">
-        <v>79221</v>
+        <v>57864</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1230,26 +1217,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1257,10 +1249,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>495992</v>
+        <v>496018</v>
       </c>
       <c r="R6" t="n">
-        <v>7016301</v>
+        <v>7016278</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1297,7 +1289,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På gran intill andra hänglavar.</t>
+          <t>Ringhack, äldre, i riklig mängd längs flera meter på en granstam. Med tydliga spår av sav/kådaflöden. Granen med ringhack står intill en enklare körväg.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1306,7 +1298,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1327,12 +1318,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1350,10 +1341,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130887121</v>
+        <v>130887090</v>
       </c>
       <c r="B7" t="n">
-        <v>79221</v>
+        <v>57864</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1361,26 +1352,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1388,10 +1384,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>495911</v>
+        <v>495983</v>
       </c>
       <c r="R7" t="n">
-        <v>7016227</v>
+        <v>7016212</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1426,13 +1422,17 @@
           <t>2026-01-26</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Välsnidat bohål på ca 1,75 meters höjd i en döende gran. Bohålets diameter är 4,5 cm.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1453,12 +1453,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1476,38 +1476,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130887108</v>
+        <v>130887094</v>
       </c>
       <c r="B8" t="n">
-        <v>97845</v>
+        <v>57864</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1515,10 +1519,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>495742</v>
+        <v>495901</v>
       </c>
       <c r="R8" t="n">
-        <v>7016070</v>
+        <v>7016223</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1553,19 +1557,43 @@
           <t>2026-01-26</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en levande något grövre gammal gran nära kant mot ungskog.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1583,42 +1611,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130887094</v>
+        <v>130887108</v>
       </c>
       <c r="B9" t="n">
-        <v>57864</v>
+        <v>97854</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1626,10 +1650,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>495901</v>
+        <v>495742</v>
       </c>
       <c r="R9" t="n">
-        <v>7016223</v>
+        <v>7016070</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1664,43 +1688,19 @@
           <t>2026-01-26</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en levande något grövre gammal gran nära kant mot ungskog.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -2766,10 +2766,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130887085</v>
+        <v>130887122</v>
       </c>
       <c r="B18" t="n">
-        <v>57864</v>
+        <v>79221</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2777,31 +2777,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2809,10 +2804,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>495713</v>
+        <v>495898</v>
       </c>
       <c r="R18" t="n">
-        <v>7015939</v>
+        <v>7016234</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2847,17 +2842,13 @@
           <t>2026-01-26</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, längs flera meter på en gran med spår efter påtagligt sav/kådaflöde.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2878,12 +2869,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2901,10 +2892,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130887122</v>
+        <v>130887085</v>
       </c>
       <c r="B19" t="n">
-        <v>79221</v>
+        <v>57864</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2912,26 +2903,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2939,10 +2935,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>495898</v>
+        <v>495713</v>
       </c>
       <c r="R19" t="n">
-        <v>7016234</v>
+        <v>7015939</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2977,13 +2973,17 @@
           <t>2026-01-26</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, längs flera meter på en gran med spår efter påtagligt sav/kådaflöde.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3027,43 +3027,40 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130887104</v>
+        <v>130887098</v>
       </c>
       <c r="B20" t="n">
-        <v>80355</v>
+        <v>57864</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -3073,10 +3070,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>495828</v>
+        <v>495849</v>
       </c>
       <c r="R20" t="n">
-        <v>7015949</v>
+        <v>7016251</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3113,7 +3110,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Bålar av stuplav som täcker ca 3 dm2 sälg.</t>
+          <t>Ringhack, äldre, längs några meter på en levande gran nära kant mot ungskog.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3122,33 +3119,32 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3166,7 +3162,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130887106</v>
+        <v>130887104</v>
       </c>
       <c r="B21" t="n">
         <v>80355</v>
@@ -3195,7 +3191,11 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr">
         <is>
           <t>med apothecier</t>
@@ -3208,10 +3208,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>495981</v>
+        <v>495828</v>
       </c>
       <c r="R21" t="n">
-        <v>7016252</v>
+        <v>7015949</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Enstaka bålar på en sälg.</t>
+          <t>Bålar av stuplav som täcker ca 3 dm2 sälg.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3263,7 +3263,7 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -3301,37 +3301,41 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130887119</v>
+        <v>130887106</v>
       </c>
       <c r="B22" t="n">
-        <v>79221</v>
+        <v>80355</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3339,10 +3343,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>495992</v>
+        <v>495981</v>
       </c>
       <c r="R22" t="n">
-        <v>7016329</v>
+        <v>7016252</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3379,7 +3383,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flera granar. Längsta bålen ca 80 cm.</t>
+          <t>Enstaka bålar på en sälg.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3399,22 +3403,22 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3432,7 +3436,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130887116</v>
+        <v>130887119</v>
       </c>
       <c r="B23" t="n">
         <v>79221</v>
@@ -3470,10 +3474,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>495725</v>
+        <v>495992</v>
       </c>
       <c r="R23" t="n">
-        <v>7016183</v>
+        <v>7016329</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3510,7 +3514,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Långväxta bålar på flera granar. Längsta bålen ca 80 cm.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3563,10 +3567,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130887098</v>
+        <v>130887116</v>
       </c>
       <c r="B24" t="n">
-        <v>57864</v>
+        <v>79221</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3574,31 +3578,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3606,10 +3605,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>495849</v>
+        <v>495725</v>
       </c>
       <c r="R24" t="n">
-        <v>7016251</v>
+        <v>7016183</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3646,7 +3645,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs några meter på en levande gran nära kant mot ungskog.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3655,6 +3654,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3675,12 +3675,12 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3698,10 +3698,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130887107</v>
+        <v>130887120</v>
       </c>
       <c r="B25" t="n">
-        <v>57861</v>
+        <v>79221</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3709,50 +3709,41 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Palleråsen Södra, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>495982</v>
+        <v>495991</v>
       </c>
       <c r="R25" t="n">
-        <v>7016398</v>
+        <v>7016264</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3789,7 +3780,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>1 eller möjligen 2 individer som sågs och hördes hacka i stående döda granar och uttryckte lockläte emellanåt. Hyfsat gott om stående död ved på/kring fyndplatsen.</t>
+          <t>Långväxta fertila bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3798,6 +3789,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3806,9 +3798,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>Äldre bitvis flerskiktad granskog.</t>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3826,10 +3833,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130887120</v>
+        <v>130887107</v>
       </c>
       <c r="B26" t="n">
-        <v>79221</v>
+        <v>57861</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3837,41 +3844,50 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Palleråsen Södra, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>495991</v>
+        <v>495982</v>
       </c>
       <c r="R26" t="n">
-        <v>7016264</v>
+        <v>7016398</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3908,7 +3924,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Långväxta fertila bålar med apothecier.</t>
+          <t>1 eller möjligen 2 individer som sågs och hördes hacka i stående döda granar och uttryckte lockläte emellanåt. Hyfsat gott om stående död ved på/kring fyndplatsen.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3917,7 +3933,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3926,24 +3941,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Äldre bitvis flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4893,7 +4893,7 @@
         <v>130887082</v>
       </c>
       <c r="B34" t="n">
-        <v>91776</v>
+        <v>91784</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5559,7 +5559,7 @@
         <v>130887109</v>
       </c>
       <c r="B39" t="n">
-        <v>97845</v>
+        <v>97854</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -6176,10 +6176,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130887124</v>
+        <v>130887087</v>
       </c>
       <c r="B44" t="n">
-        <v>79221</v>
+        <v>57864</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6187,26 +6187,31 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -6214,10 +6219,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>495877</v>
+        <v>495680</v>
       </c>
       <c r="R44" t="n">
-        <v>7016270</v>
+        <v>7016064</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6254,7 +6259,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Ringhack, färska, på en högväxt gran intill en mindre väg.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6263,7 +6268,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -6284,12 +6288,12 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6307,10 +6311,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130887129</v>
+        <v>130887097</v>
       </c>
       <c r="B45" t="n">
-        <v>79221</v>
+        <v>57864</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6318,26 +6322,31 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -6345,10 +6354,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>495878</v>
+        <v>495856</v>
       </c>
       <c r="R45" t="n">
-        <v>7016320</v>
+        <v>7016255</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6383,13 +6392,17 @@
           <t>2026-01-26</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, längs flera meter långt upp på en levande gran nära kant mot ungskog. Tydliga spår av sav/kådaflöde på granens stam.</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -6410,12 +6423,12 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6433,10 +6446,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130887081</v>
+        <v>130887091</v>
       </c>
       <c r="B46" t="n">
-        <v>91776</v>
+        <v>57864</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6444,28 +6457,29 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
@@ -6475,10 +6489,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>495919</v>
+        <v>495967</v>
       </c>
       <c r="R46" t="n">
-        <v>7016205</v>
+        <v>7016170</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6515,7 +6529,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>I upplyft granlåga.</t>
+          <t>Ringhack, färska, på en levande gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6524,7 +6538,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -6545,12 +6558,12 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6568,10 +6581,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130887087</v>
+        <v>130887081</v>
       </c>
       <c r="B47" t="n">
-        <v>57864</v>
+        <v>91784</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6579,29 +6592,28 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
@@ -6611,10 +6623,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>495680</v>
+        <v>495919</v>
       </c>
       <c r="R47" t="n">
-        <v>7016064</v>
+        <v>7016205</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6651,7 +6663,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en högväxt gran intill en mindre väg.</t>
+          <t>I upplyft granlåga.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6660,6 +6672,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6680,12 +6693,12 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6703,10 +6716,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130887097</v>
+        <v>130887124</v>
       </c>
       <c r="B48" t="n">
-        <v>57864</v>
+        <v>79221</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6714,31 +6727,26 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6746,10 +6754,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>495856</v>
+        <v>495877</v>
       </c>
       <c r="R48" t="n">
-        <v>7016255</v>
+        <v>7016270</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6786,7 +6794,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs flera meter långt upp på en levande gran nära kant mot ungskog. Tydliga spår av sav/kådaflöde på granens stam.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6795,6 +6803,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6815,12 +6824,12 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6838,10 +6847,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130887091</v>
+        <v>130887129</v>
       </c>
       <c r="B49" t="n">
-        <v>57864</v>
+        <v>79221</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6849,31 +6858,26 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6881,10 +6885,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>495967</v>
+        <v>495878</v>
       </c>
       <c r="R49" t="n">
-        <v>7016170</v>
+        <v>7016320</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6919,17 +6923,13 @@
           <t>2026-01-26</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en levande gran vid en hyggeskant.</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6950,12 +6950,12 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>

--- a/artfynd/A 62696-2025 artfynd.xlsx
+++ b/artfynd/A 62696-2025 artfynd.xlsx
@@ -1206,7 +1206,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130887089</v>
+        <v>130887090</v>
       </c>
       <c r="B6" t="n">
         <v>57864</v>
@@ -1239,7 +1239,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>496018</v>
+        <v>495983</v>
       </c>
       <c r="R6" t="n">
-        <v>7016278</v>
+        <v>7016212</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, i riklig mängd längs flera meter på en granstam. Med tydliga spår av sav/kådaflöden. Granen med ringhack står intill en enklare körväg.</t>
+          <t>Välsnidat bohål på ca 1,75 meters höjd i en döende gran. Bohålets diameter är 4,5 cm.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1341,7 +1341,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130887090</v>
+        <v>130887089</v>
       </c>
       <c r="B7" t="n">
         <v>57864</v>
@@ -1374,7 +1374,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1384,10 +1384,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>495983</v>
+        <v>496018</v>
       </c>
       <c r="R7" t="n">
-        <v>7016212</v>
+        <v>7016278</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Välsnidat bohål på ca 1,75 meters höjd i en döende gran. Bohålets diameter är 4,5 cm.</t>
+          <t>Ringhack, äldre, i riklig mängd längs flera meter på en granstam. Med tydliga spår av sav/kådaflöden. Granen med ringhack står intill en enklare körväg.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -3027,40 +3027,43 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130887098</v>
+        <v>130887104</v>
       </c>
       <c r="B20" t="n">
-        <v>57864</v>
+        <v>80355</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -3070,10 +3073,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>495849</v>
+        <v>495828</v>
       </c>
       <c r="R20" t="n">
-        <v>7016251</v>
+        <v>7015949</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3110,7 +3113,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs några meter på en levande gran nära kant mot ungskog.</t>
+          <t>Bålar av stuplav som täcker ca 3 dm2 sälg.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3119,32 +3122,33 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3162,7 +3166,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130887104</v>
+        <v>130887106</v>
       </c>
       <c r="B21" t="n">
         <v>80355</v>
@@ -3191,11 +3195,7 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>med apothecier</t>
@@ -3208,10 +3208,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>495828</v>
+        <v>495981</v>
       </c>
       <c r="R21" t="n">
-        <v>7015949</v>
+        <v>7016252</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Bålar av stuplav som täcker ca 3 dm2 sälg.</t>
+          <t>Enstaka bålar på en sälg.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3263,7 +3263,7 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -3301,41 +3301,37 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130887106</v>
+        <v>130887119</v>
       </c>
       <c r="B22" t="n">
-        <v>80355</v>
+        <v>79221</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3343,10 +3339,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>495981</v>
+        <v>495992</v>
       </c>
       <c r="R22" t="n">
-        <v>7016252</v>
+        <v>7016329</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3383,7 +3379,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Enstaka bålar på en sälg.</t>
+          <t>Långväxta bålar på flera granar. Längsta bålen ca 80 cm.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3403,22 +3399,22 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3436,7 +3432,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130887119</v>
+        <v>130887116</v>
       </c>
       <c r="B23" t="n">
         <v>79221</v>
@@ -3474,10 +3470,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>495992</v>
+        <v>495725</v>
       </c>
       <c r="R23" t="n">
-        <v>7016329</v>
+        <v>7016183</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3514,7 +3510,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flera granar. Längsta bålen ca 80 cm.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3567,10 +3563,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130887116</v>
+        <v>130887098</v>
       </c>
       <c r="B24" t="n">
-        <v>79221</v>
+        <v>57864</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3578,26 +3574,31 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3605,10 +3606,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>495725</v>
+        <v>495849</v>
       </c>
       <c r="R24" t="n">
-        <v>7016183</v>
+        <v>7016251</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3645,7 +3646,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Ringhack, äldre, längs några meter på en levande gran nära kant mot ungskog.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3654,7 +3655,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3675,12 +3675,12 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3698,10 +3698,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130887120</v>
+        <v>130887107</v>
       </c>
       <c r="B25" t="n">
-        <v>79221</v>
+        <v>57861</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3709,41 +3709,50 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Palleråsen Södra, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>495991</v>
+        <v>495982</v>
       </c>
       <c r="R25" t="n">
-        <v>7016264</v>
+        <v>7016398</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3780,7 +3789,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Långväxta fertila bålar med apothecier.</t>
+          <t>1 eller möjligen 2 individer som sågs och hördes hacka i stående döda granar och uttryckte lockläte emellanåt. Hyfsat gott om stående död ved på/kring fyndplatsen.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3789,7 +3798,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3798,24 +3806,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Äldre bitvis flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3833,10 +3826,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130887107</v>
+        <v>130887120</v>
       </c>
       <c r="B26" t="n">
-        <v>57861</v>
+        <v>79221</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3844,50 +3837,41 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Palleråsen Södra, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>495982</v>
+        <v>495991</v>
       </c>
       <c r="R26" t="n">
-        <v>7016398</v>
+        <v>7016264</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3924,7 +3908,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>1 eller möjligen 2 individer som sågs och hördes hacka i stående döda granar och uttryckte lockläte emellanåt. Hyfsat gott om stående död ved på/kring fyndplatsen.</t>
+          <t>Långväxta fertila bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3933,6 +3917,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3941,9 +3926,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>Äldre bitvis flerskiktad granskog.</t>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4223,10 +4223,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130887132</v>
+        <v>130887086</v>
       </c>
       <c r="B29" t="n">
-        <v>79221</v>
+        <v>57864</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4234,26 +4234,31 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -4261,10 +4266,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>496008</v>
+        <v>495683</v>
       </c>
       <c r="R29" t="n">
-        <v>7016340</v>
+        <v>7016064</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4301,7 +4306,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran. Ca 50 cm lång hängande bål.</t>
+          <t>Ringhack, färska, på en gran nära en mindre väg.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4310,7 +4315,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4331,12 +4335,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4354,7 +4358,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130887127</v>
+        <v>130887132</v>
       </c>
       <c r="B30" t="n">
         <v>79221</v>
@@ -4392,10 +4396,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>495831</v>
+        <v>496008</v>
       </c>
       <c r="R30" t="n">
-        <v>7016258</v>
+        <v>7016340</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4432,7 +4436,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På en gren av gran på ca 2 m höjd.</t>
+          <t>Långväxta bålar på gran. Ca 50 cm lång hängande bål.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4485,10 +4489,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130887096</v>
+        <v>130887127</v>
       </c>
       <c r="B31" t="n">
-        <v>57864</v>
+        <v>79221</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4496,31 +4500,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4528,10 +4527,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>495870</v>
+        <v>495831</v>
       </c>
       <c r="R31" t="n">
-        <v>7016247</v>
+        <v>7016258</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4568,7 +4567,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en levande gran nära kant mot ungskog.</t>
+          <t>På en gren av gran på ca 2 m höjd.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4577,6 +4576,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4597,12 +4597,12 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4620,7 +4620,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130887086</v>
+        <v>130887096</v>
       </c>
       <c r="B32" t="n">
         <v>57864</v>
@@ -4653,7 +4653,7 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -4663,10 +4663,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>495683</v>
+        <v>495870</v>
       </c>
       <c r="R32" t="n">
-        <v>7016064</v>
+        <v>7016247</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4703,7 +4703,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran nära en mindre väg.</t>
+          <t>Ringhack, äldre, på en levande gran nära kant mot ungskog.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -5663,7 +5663,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130887131</v>
+        <v>130887115</v>
       </c>
       <c r="B40" t="n">
         <v>79221</v>
@@ -5701,10 +5701,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>495960</v>
+        <v>495626</v>
       </c>
       <c r="R40" t="n">
-        <v>7016325</v>
+        <v>7015955</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5739,11 +5739,6 @@
           <t>2026-01-26</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>På gran i äldre granskog.</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5771,12 +5766,12 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5794,7 +5789,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130887115</v>
+        <v>130887131</v>
       </c>
       <c r="B41" t="n">
         <v>79221</v>
@@ -5832,10 +5827,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>495626</v>
+        <v>495960</v>
       </c>
       <c r="R41" t="n">
-        <v>7015955</v>
+        <v>7016325</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5870,6 +5865,11 @@
           <t>2026-01-26</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På gran i äldre granskog.</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5897,12 +5897,12 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -6176,10 +6176,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130887087</v>
+        <v>130887081</v>
       </c>
       <c r="B44" t="n">
-        <v>57864</v>
+        <v>91784</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6187,29 +6187,28 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -6219,10 +6218,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>495680</v>
+        <v>495919</v>
       </c>
       <c r="R44" t="n">
-        <v>7016064</v>
+        <v>7016205</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6259,7 +6258,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en högväxt gran intill en mindre väg.</t>
+          <t>I upplyft granlåga.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6268,6 +6267,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -6288,12 +6288,12 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6311,10 +6311,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130887097</v>
+        <v>130887124</v>
       </c>
       <c r="B45" t="n">
-        <v>57864</v>
+        <v>79221</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6322,31 +6322,26 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -6354,10 +6349,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>495856</v>
+        <v>495877</v>
       </c>
       <c r="R45" t="n">
-        <v>7016255</v>
+        <v>7016270</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6394,7 +6389,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs flera meter långt upp på en levande gran nära kant mot ungskog. Tydliga spår av sav/kådaflöde på granens stam.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6403,6 +6398,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -6423,12 +6419,12 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6446,7 +6442,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130887091</v>
+        <v>130887087</v>
       </c>
       <c r="B46" t="n">
         <v>57864</v>
@@ -6489,10 +6485,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>495967</v>
+        <v>495680</v>
       </c>
       <c r="R46" t="n">
-        <v>7016170</v>
+        <v>7016064</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6529,7 +6525,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en levande gran vid en hyggeskant.</t>
+          <t>Ringhack, färska, på en högväxt gran intill en mindre väg.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6581,10 +6577,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130887081</v>
+        <v>130887129</v>
       </c>
       <c r="B47" t="n">
-        <v>91784</v>
+        <v>79221</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6592,30 +6588,26 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6623,10 +6615,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>495919</v>
+        <v>495878</v>
       </c>
       <c r="R47" t="n">
-        <v>7016205</v>
+        <v>7016320</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6661,11 +6653,6 @@
           <t>2026-01-26</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>I upplyft granlåga.</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -6693,12 +6680,12 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6716,10 +6703,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130887124</v>
+        <v>130887097</v>
       </c>
       <c r="B48" t="n">
-        <v>79221</v>
+        <v>57864</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6727,26 +6714,31 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6754,10 +6746,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>495877</v>
+        <v>495856</v>
       </c>
       <c r="R48" t="n">
-        <v>7016270</v>
+        <v>7016255</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6794,7 +6786,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Ringhack, äldre, längs flera meter långt upp på en levande gran nära kant mot ungskog. Tydliga spår av sav/kådaflöde på granens stam.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6803,7 +6795,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6824,12 +6815,12 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6847,10 +6838,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130887129</v>
+        <v>130887091</v>
       </c>
       <c r="B49" t="n">
-        <v>79221</v>
+        <v>57864</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6858,26 +6849,31 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6885,10 +6881,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>495878</v>
+        <v>495967</v>
       </c>
       <c r="R49" t="n">
-        <v>7016320</v>
+        <v>7016170</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6923,13 +6919,17 @@
           <t>2026-01-26</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en levande gran vid en hyggeskant.</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6950,12 +6950,12 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>

--- a/artfynd/A 62696-2025 artfynd.xlsx
+++ b/artfynd/A 62696-2025 artfynd.xlsx
@@ -675,57 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130887083</v>
+        <v>130887112</v>
       </c>
       <c r="B2" t="n">
-        <v>57884</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Palleråsen Södra, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>495881</v>
+        <v>495735</v>
       </c>
       <c r="R2" t="n">
-        <v>7015990</v>
+        <v>7016071</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,7 +753,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, enstaka några meter upp på en gran intill en glänta.</t>
+          <t>Enstaka bålar på gran.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,6 +762,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -791,12 +783,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -814,42 +806,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130887092</v>
+        <v>130887113</v>
       </c>
       <c r="B3" t="n">
-        <v>57884</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -857,10 +844,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>495933</v>
+        <v>495718</v>
       </c>
       <c r="R3" t="n">
-        <v>7016163</v>
+        <v>7015966</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,23 +882,19 @@
           <t>2026-01-26</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en levande gran nära kant mot ungskog.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -926,12 +909,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -949,42 +932,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130887089</v>
+        <v>130887114</v>
       </c>
       <c r="B4" t="n">
-        <v>57884</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -992,10 +970,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>496018</v>
+        <v>495689</v>
       </c>
       <c r="R4" t="n">
-        <v>7016278</v>
+        <v>7015994</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1030,17 +1008,13 @@
           <t>2026-01-26</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, i riklig mängd längs flera meter på en granstam. Med tydliga spår av sav/kådaflöden. Granen med ringhack står intill en enklare körväg.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1061,12 +1035,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1084,42 +1058,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130887090</v>
+        <v>130887115</v>
       </c>
       <c r="B5" t="n">
-        <v>57884</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1127,10 +1096,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>495983</v>
+        <v>495626</v>
       </c>
       <c r="R5" t="n">
-        <v>7016212</v>
+        <v>7015955</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1165,17 +1134,13 @@
           <t>2026-01-26</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Välsnidat bohål på ca 1,75 meters höjd i en döende gran. Bohålets diameter är 4,5 cm.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1196,12 +1161,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1219,14 +1184,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130887118</v>
+        <v>130887117</v>
       </c>
       <c r="B6" t="n">
-        <v>79245</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1257,10 +1222,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>495992</v>
+        <v>495769</v>
       </c>
       <c r="R6" t="n">
-        <v>7016301</v>
+        <v>7016151</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1297,7 +1262,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På gran intill andra hänglavar.</t>
+          <t>Växer på en hyfsat grovbarkig gammal gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1350,37 +1315,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130887121</v>
+        <v>130887104</v>
       </c>
       <c r="B7" t="n">
-        <v>79245</v>
+        <v>80461</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1388,10 +1361,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>495911</v>
+        <v>495828</v>
       </c>
       <c r="R7" t="n">
-        <v>7016227</v>
+        <v>7015949</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1426,6 +1399,11 @@
           <t>2026-01-26</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Bålar av stuplav som täcker ca 3 dm2 sälg.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1438,27 +1416,27 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1476,40 +1454,39 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130887094</v>
+        <v>130887105</v>
       </c>
       <c r="B8" t="n">
-        <v>57884</v>
+        <v>80461</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1519,10 +1496,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>495901</v>
+        <v>495736</v>
       </c>
       <c r="R8" t="n">
-        <v>7016223</v>
+        <v>7016168</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1557,17 +1534,13 @@
           <t>2026-01-26</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en levande något grövre gammal gran nära kant mot ungskog.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1578,22 +1551,22 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1611,49 +1584,57 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130887108</v>
+        <v>130887083</v>
       </c>
       <c r="B9" t="n">
-        <v>97880</v>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Palleråsen Södra, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>495742</v>
+        <v>495881</v>
       </c>
       <c r="R9" t="n">
-        <v>7016070</v>
+        <v>7015990</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1688,19 +1669,43 @@
           <t>2026-01-26</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, enstaka några meter upp på en gran intill en glänta.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1718,10 +1723,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130887100</v>
+        <v>130887084</v>
       </c>
       <c r="B10" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1751,20 +1756,24 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Palleråsen Södra, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>495805</v>
+        <v>495868</v>
       </c>
       <c r="R10" t="n">
-        <v>7016271</v>
+        <v>7015959</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1801,7 +1810,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en levande gran vid kanten mot ungskog. Spår av sav/kådaflöde på granens stam.</t>
+          <t>Ringhack, färska, enstaka några meter upp på en granstam vid en glänta.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1853,10 +1862,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130887088</v>
+        <v>130887085</v>
       </c>
       <c r="B11" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1886,24 +1895,20 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Palleråsen Södra, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>495679</v>
+        <v>495713</v>
       </c>
       <c r="R11" t="n">
-        <v>7016071</v>
+        <v>7015939</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1940,7 +1945,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran intill en mindre väg.</t>
+          <t>Ringhack, äldre, längs flera meter på en gran med spår efter påtagligt sav/kådaflöde.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1992,10 +1997,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130887102</v>
+        <v>130887086</v>
       </c>
       <c r="B12" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2025,7 +2030,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -2035,10 +2040,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>495951</v>
+        <v>495683</v>
       </c>
       <c r="R12" t="n">
-        <v>7016339</v>
+        <v>7016064</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2075,14 +2080,14 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Gammalt bohål på 2 meters höjd i en stående död gran. Bohålet är 5 cm i diameter längst ut och ca 4 cm i diameter en bit in i ingångshålet. Ev. skapat av tretåig hackspett. Stående död ved som indikerar högt livsmiljövärde för tretåig hackspett finns på/kring fyndplatsen.</t>
+          <t>Ringhack, färska, på en gran nära en mindre väg.</t>
         </is>
       </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="b">
         <v>0</v>
@@ -2127,10 +2132,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130887126</v>
+        <v>130887087</v>
       </c>
       <c r="B13" t="n">
-        <v>79245</v>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2138,26 +2143,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2165,10 +2175,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>495942</v>
+        <v>495680</v>
       </c>
       <c r="R13" t="n">
-        <v>7016269</v>
+        <v>7016064</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2203,13 +2213,17 @@
           <t>2026-01-26</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en högväxt gran intill en mindre väg.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2230,12 +2244,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2253,10 +2267,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130887133</v>
+        <v>130887088</v>
       </c>
       <c r="B14" t="n">
-        <v>79245</v>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2264,37 +2278,46 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Palleråsen Södra, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>496017</v>
+        <v>495679</v>
       </c>
       <c r="R14" t="n">
-        <v>7016363</v>
+        <v>7016071</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2329,13 +2352,17 @@
           <t>2026-01-26</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran intill en mindre väg.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2356,12 +2383,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2379,10 +2406,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130887123</v>
+        <v>130887091</v>
       </c>
       <c r="B15" t="n">
-        <v>79245</v>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2390,26 +2417,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2417,10 +2449,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>495877</v>
+        <v>495967</v>
       </c>
       <c r="R15" t="n">
-        <v>7016242</v>
+        <v>7016170</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2455,13 +2487,17 @@
           <t>2026-01-26</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en levande gran vid en hyggeskant.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2482,12 +2518,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2505,10 +2541,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130887095</v>
+        <v>130887092</v>
       </c>
       <c r="B16" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2548,10 +2584,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>495890</v>
+        <v>495933</v>
       </c>
       <c r="R16" t="n">
-        <v>7016236</v>
+        <v>7016163</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2588,7 +2624,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, enstaka högt upp på stammen av en levande gran nära kant mot ungskog.</t>
+          <t>Ringhack, äldre, på en levande gran nära kant mot ungskog.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2640,10 +2676,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130887125</v>
+        <v>130887093</v>
       </c>
       <c r="B17" t="n">
-        <v>79245</v>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2651,26 +2687,31 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2678,10 +2719,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>495945</v>
+        <v>495930</v>
       </c>
       <c r="R17" t="n">
-        <v>7016232</v>
+        <v>7016165</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2716,13 +2757,17 @@
           <t>2026-01-26</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre, på låg höjd på en levande mer klen gran nära kant mot ungskog.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2743,12 +2788,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2766,42 +2811,38 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130887085</v>
+        <v>130887108</v>
       </c>
       <c r="B18" t="n">
-        <v>57884</v>
+        <v>97983</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2809,10 +2850,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>495713</v>
+        <v>495742</v>
       </c>
       <c r="R18" t="n">
-        <v>7015939</v>
+        <v>7016070</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2847,43 +2888,19 @@
           <t>2026-01-26</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, längs flera meter på en gran med spår efter påtagligt sav/kådaflöde.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2901,10 +2918,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130887122</v>
+        <v>130887081</v>
       </c>
       <c r="B19" t="n">
-        <v>79245</v>
+        <v>91909</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2912,26 +2929,30 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2939,10 +2960,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>495898</v>
+        <v>495919</v>
       </c>
       <c r="R19" t="n">
-        <v>7016234</v>
+        <v>7016205</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2977,6 +2998,11 @@
           <t>2026-01-26</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>I upplyft granlåga.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -3004,12 +3030,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3027,10 +3053,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130887098</v>
+        <v>130887082</v>
       </c>
       <c r="B20" t="n">
-        <v>57884</v>
+        <v>91909</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3038,29 +3064,28 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -3070,10 +3095,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>495849</v>
+        <v>495948</v>
       </c>
       <c r="R20" t="n">
-        <v>7016251</v>
+        <v>7016328</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3110,7 +3135,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs några meter på en levande gran nära kant mot ungskog.</t>
+          <t>Rikligt med fruktkroppar i en upplyft granlåga.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3119,6 +3144,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3139,12 +3165,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3162,45 +3188,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130887104</v>
+        <v>130887116</v>
       </c>
       <c r="B21" t="n">
-        <v>80379</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3208,10 +3226,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>495828</v>
+        <v>495725</v>
       </c>
       <c r="R21" t="n">
-        <v>7015949</v>
+        <v>7016183</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3248,7 +3266,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Bålar av stuplav som täcker ca 3 dm2 sälg.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3263,27 +3281,27 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3301,41 +3319,37 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130887106</v>
+        <v>130887118</v>
       </c>
       <c r="B22" t="n">
-        <v>80379</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3343,10 +3357,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>495981</v>
+        <v>495992</v>
       </c>
       <c r="R22" t="n">
-        <v>7016252</v>
+        <v>7016301</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3383,7 +3397,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Enstaka bålar på en sälg.</t>
+          <t>På gran intill andra hänglavar.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3403,22 +3417,22 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3439,11 +3453,11 @@
         <v>130887119</v>
       </c>
       <c r="B23" t="n">
-        <v>79245</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -3567,14 +3581,14 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130887116</v>
+        <v>130887120</v>
       </c>
       <c r="B24" t="n">
-        <v>79245</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -3597,7 +3611,11 @@
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3605,10 +3623,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>495725</v>
+        <v>495991</v>
       </c>
       <c r="R24" t="n">
-        <v>7016183</v>
+        <v>7016264</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3645,7 +3663,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Långväxta fertila bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3698,61 +3716,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130887107</v>
+        <v>130887121</v>
       </c>
       <c r="B25" t="n">
-        <v>57881</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Palleråsen Södra, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>495982</v>
+        <v>495911</v>
       </c>
       <c r="R25" t="n">
-        <v>7016398</v>
+        <v>7016227</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3787,17 +3792,13 @@
           <t>2026-01-26</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>1 eller möjligen 2 individer som sågs och hördes hacka i stående döda granar och uttryckte lockläte emellanåt. Hyfsat gott om stående död ved på/kring fyndplatsen.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3806,9 +3807,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>Äldre bitvis flerskiktad granskog.</t>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3826,14 +3842,14 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130887120</v>
+        <v>130887122</v>
       </c>
       <c r="B26" t="n">
-        <v>79245</v>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -3856,11 +3872,7 @@
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3868,10 +3880,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>495991</v>
+        <v>495898</v>
       </c>
       <c r="R26" t="n">
-        <v>7016264</v>
+        <v>7016234</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3904,11 +3916,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-01-26</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Långväxta fertila bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3961,14 +3968,14 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130887130</v>
+        <v>130887123</v>
       </c>
       <c r="B27" t="n">
-        <v>79245</v>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -3999,10 +4006,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>495946</v>
+        <v>495877</v>
       </c>
       <c r="R27" t="n">
-        <v>7016297</v>
+        <v>7016242</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4037,11 +4044,6 @@
           <t>2026-01-26</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Växer på en stående död gran med full längd.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -4069,12 +4071,12 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4092,14 +4094,14 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130887128</v>
+        <v>130887124</v>
       </c>
       <c r="B28" t="n">
-        <v>79245</v>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -4130,10 +4132,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>495815</v>
+        <v>495877</v>
       </c>
       <c r="R28" t="n">
-        <v>7016313</v>
+        <v>7016270</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4170,7 +4172,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Bland andra hänglavar på gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4223,42 +4225,37 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130887086</v>
+        <v>130887125</v>
       </c>
       <c r="B29" t="n">
-        <v>57884</v>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -4266,10 +4263,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>495683</v>
+        <v>495945</v>
       </c>
       <c r="R29" t="n">
-        <v>7016064</v>
+        <v>7016232</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4304,17 +4301,13 @@
           <t>2026-01-26</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran nära en mindre väg.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4335,12 +4328,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4358,42 +4351,37 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130887096</v>
+        <v>130887126</v>
       </c>
       <c r="B30" t="n">
-        <v>57884</v>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4401,10 +4389,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>495870</v>
+        <v>495942</v>
       </c>
       <c r="R30" t="n">
-        <v>7016247</v>
+        <v>7016269</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4439,17 +4427,13 @@
           <t>2026-01-26</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en levande gran nära kant mot ungskog.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4470,12 +4454,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4493,14 +4477,14 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130887132</v>
+        <v>130887127</v>
       </c>
       <c r="B31" t="n">
-        <v>79245</v>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -4531,10 +4515,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>496008</v>
+        <v>495831</v>
       </c>
       <c r="R31" t="n">
-        <v>7016340</v>
+        <v>7016258</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4571,7 +4555,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran. Ca 50 cm lång hängande bål.</t>
+          <t>På en gren av gran på ca 2 m höjd.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4624,14 +4608,14 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130887127</v>
+        <v>130887128</v>
       </c>
       <c r="B32" t="n">
-        <v>79245</v>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -4662,10 +4646,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>495831</v>
+        <v>495815</v>
       </c>
       <c r="R32" t="n">
-        <v>7016258</v>
+        <v>7016313</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4702,7 +4686,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På en gren av gran på ca 2 m höjd.</t>
+          <t>Bland andra hänglavar på gran.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4755,42 +4739,37 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130887093</v>
+        <v>130887129</v>
       </c>
       <c r="B33" t="n">
-        <v>57884</v>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4798,10 +4777,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>495930</v>
+        <v>495878</v>
       </c>
       <c r="R33" t="n">
-        <v>7016165</v>
+        <v>7016320</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4836,17 +4815,13 @@
           <t>2026-01-26</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre, på låg höjd på en levande mer klen gran nära kant mot ungskog.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4867,12 +4842,12 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4890,41 +4865,37 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130887082</v>
+        <v>130887130</v>
       </c>
       <c r="B34" t="n">
-        <v>91810</v>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4932,10 +4903,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>495948</v>
+        <v>495946</v>
       </c>
       <c r="R34" t="n">
-        <v>7016328</v>
+        <v>7016297</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4972,7 +4943,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Rikligt med fruktkroppar i en upplyft granlåga.</t>
+          <t>Växer på en stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5002,12 +4973,12 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5025,14 +4996,14 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130887113</v>
+        <v>130887131</v>
       </c>
       <c r="B35" t="n">
-        <v>79245</v>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -5063,10 +5034,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>495718</v>
+        <v>495960</v>
       </c>
       <c r="R35" t="n">
-        <v>7015966</v>
+        <v>7016325</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5101,6 +5072,11 @@
           <t>2026-01-26</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>På gran i äldre granskog.</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -5113,7 +5089,7 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
@@ -5128,12 +5104,12 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5151,14 +5127,14 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130887117</v>
+        <v>130887132</v>
       </c>
       <c r="B36" t="n">
-        <v>79245</v>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -5189,10 +5165,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>495769</v>
+        <v>496008</v>
       </c>
       <c r="R36" t="n">
-        <v>7016151</v>
+        <v>7016340</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5229,7 +5205,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Växer på en hyfsat grovbarkig gammal gran.</t>
+          <t>Långväxta bålar på gran. Ca 50 cm lång hängande bål.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5282,57 +5258,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130887084</v>
+        <v>130887133</v>
       </c>
       <c r="B37" t="n">
-        <v>57884</v>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Palleråsen Södra, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>495868</v>
+        <v>496017</v>
       </c>
       <c r="R37" t="n">
-        <v>7015959</v>
+        <v>7016363</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5367,17 +5334,13 @@
           <t>2026-01-26</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, enstaka några meter upp på en granstam vid en glänta.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -5398,12 +5361,12 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5421,40 +5384,39 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130887099</v>
+        <v>130887106</v>
       </c>
       <c r="B38" t="n">
-        <v>57884</v>
+        <v>80461</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -5464,10 +5426,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>495812</v>
+        <v>495981</v>
       </c>
       <c r="R38" t="n">
-        <v>7016273</v>
+        <v>7016252</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5504,7 +5466,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en levande gran nära kant mot ungskog.</t>
+          <t>Enstaka bålar på en sälg.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5513,6 +5475,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5523,22 +5486,22 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5556,10 +5519,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130887109</v>
+        <v>130887107</v>
       </c>
       <c r="B39" t="n">
-        <v>97880</v>
+        <v>57950</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5567,38 +5530,50 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Palleråsen Södra, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>496004</v>
+        <v>495982</v>
       </c>
       <c r="R39" t="n">
-        <v>7016371</v>
+        <v>7016398</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5633,19 +5608,28 @@
           <t>2026-01-26</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>1 eller möjligen 2 individer som sågs och hördes hacka i stående döda granar och uttryckte lockläte emellanåt. Hyfsat gott om stående död ved på/kring fyndplatsen.</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>Äldre bitvis flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5663,10 +5647,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130887131</v>
+        <v>130887089</v>
       </c>
       <c r="B40" t="n">
-        <v>79245</v>
+        <v>57953</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5674,26 +5658,31 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5701,10 +5690,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>495960</v>
+        <v>496018</v>
       </c>
       <c r="R40" t="n">
-        <v>7016325</v>
+        <v>7016278</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5741,7 +5730,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På gran i äldre granskog.</t>
+          <t>Ringhack, äldre, i riklig mängd längs flera meter på en granstam. Med tydliga spår av sav/kådaflöden. Granen med ringhack står intill en enklare körväg.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5750,7 +5739,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5794,10 +5782,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130887115</v>
+        <v>130887090</v>
       </c>
       <c r="B41" t="n">
-        <v>79245</v>
+        <v>57953</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5805,26 +5793,31 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5832,10 +5825,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>495626</v>
+        <v>495983</v>
       </c>
       <c r="R41" t="n">
-        <v>7015955</v>
+        <v>7016212</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5870,13 +5863,17 @@
           <t>2026-01-26</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Välsnidat bohål på ca 1,75 meters höjd i en döende gran. Bohålets diameter är 4,5 cm.</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5897,12 +5894,12 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5920,10 +5917,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130887114</v>
+        <v>130887094</v>
       </c>
       <c r="B42" t="n">
-        <v>79245</v>
+        <v>57953</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5931,26 +5928,31 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5958,10 +5960,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>495689</v>
+        <v>495901</v>
       </c>
       <c r="R42" t="n">
-        <v>7015994</v>
+        <v>7016223</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5996,13 +5998,17 @@
           <t>2026-01-26</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en levande något grövre gammal gran nära kant mot ungskog.</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -6023,12 +6029,12 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6046,39 +6052,40 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130887105</v>
+        <v>130887095</v>
       </c>
       <c r="B43" t="n">
-        <v>80379</v>
+        <v>57953</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -6088,10 +6095,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>495736</v>
+        <v>495890</v>
       </c>
       <c r="R43" t="n">
-        <v>7016168</v>
+        <v>7016236</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6126,13 +6133,17 @@
           <t>2026-01-26</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, enstaka högt upp på stammen av en levande gran nära kant mot ungskog.</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -6143,22 +6154,22 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6176,10 +6187,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130887091</v>
+        <v>130887096</v>
       </c>
       <c r="B44" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6209,7 +6220,7 @@
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -6219,10 +6230,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>495967</v>
+        <v>495870</v>
       </c>
       <c r="R44" t="n">
-        <v>7016170</v>
+        <v>7016247</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6259,7 +6270,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en levande gran vid en hyggeskant.</t>
+          <t>Ringhack, äldre, på en levande gran nära kant mot ungskog.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6311,10 +6322,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130887081</v>
+        <v>130887097</v>
       </c>
       <c r="B45" t="n">
-        <v>91810</v>
+        <v>57953</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6322,28 +6333,29 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -6353,10 +6365,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>495919</v>
+        <v>495856</v>
       </c>
       <c r="R45" t="n">
-        <v>7016205</v>
+        <v>7016255</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6393,7 +6405,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>I upplyft granlåga.</t>
+          <t>Ringhack, äldre, längs flera meter långt upp på en levande gran nära kant mot ungskog. Tydliga spår av sav/kådaflöde på granens stam.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6402,7 +6414,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -6423,12 +6434,12 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6446,10 +6457,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130887087</v>
+        <v>130887098</v>
       </c>
       <c r="B46" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6479,7 +6490,7 @@
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
@@ -6489,10 +6500,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>495680</v>
+        <v>495849</v>
       </c>
       <c r="R46" t="n">
-        <v>7016064</v>
+        <v>7016251</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6529,7 +6540,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en högväxt gran intill en mindre väg.</t>
+          <t>Ringhack, äldre, längs några meter på en levande gran nära kant mot ungskog.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6581,10 +6592,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130887097</v>
+        <v>130887099</v>
       </c>
       <c r="B47" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6624,10 +6635,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>495856</v>
+        <v>495812</v>
       </c>
       <c r="R47" t="n">
-        <v>7016255</v>
+        <v>7016273</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6664,7 +6675,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs flera meter långt upp på en levande gran nära kant mot ungskog. Tydliga spår av sav/kådaflöde på granens stam.</t>
+          <t>Ringhack, äldre, på en levande gran nära kant mot ungskog.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6716,10 +6727,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130887124</v>
+        <v>130887100</v>
       </c>
       <c r="B48" t="n">
-        <v>79245</v>
+        <v>57953</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6727,26 +6738,31 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6754,10 +6770,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>495877</v>
+        <v>495805</v>
       </c>
       <c r="R48" t="n">
-        <v>7016270</v>
+        <v>7016271</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6794,7 +6810,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Ringhack, äldre, på en levande gran vid kanten mot ungskog. Spår av sav/kådaflöde på granens stam.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6803,7 +6819,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6824,12 +6839,12 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6847,10 +6862,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130887129</v>
+        <v>130887101</v>
       </c>
       <c r="B49" t="n">
-        <v>79245</v>
+        <v>57953</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6858,37 +6873,46 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Palleråsen Södra, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>495878</v>
+        <v>495852</v>
       </c>
       <c r="R49" t="n">
-        <v>7016320</v>
+        <v>7016315</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6923,13 +6947,17 @@
           <t>2026-01-26</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, längs ca 3 meter på en levande gran vid en lucka i skogen. En volym av stående död ved av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett på fyndplatsen.</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6938,6 +6966,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>Äldre bitvis flerskiktad granskog med inslag av tall, björk, sälg och gråal.</t>
+        </is>
+      </c>
       <c r="AJ49" t="inlineStr">
         <is>
           <t>gran</t>
@@ -6950,12 +6983,12 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6973,10 +7006,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130887101</v>
+        <v>130887102</v>
       </c>
       <c r="B50" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -7006,24 +7039,20 @@
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Palleråsen Södra, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>495852</v>
+        <v>495951</v>
       </c>
       <c r="R50" t="n">
-        <v>7016315</v>
+        <v>7016339</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -7060,14 +7089,14 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack, färska, längs ca 3 meter på en levande gran vid en lucka i skogen. En volym av stående död ved av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett på fyndplatsen.</t>
+          <t>Gammalt bohål på 2 meters höjd i en stående död gran. Bohålet är 5 cm i diameter längst ut och ca 4 cm i diameter en bit in i ingångshålet. Ev. skapat av tretåig hackspett. Stående död ved som indikerar högt livsmiljövärde för tretåig hackspett finns på/kring fyndplatsen.</t>
         </is>
       </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG50" t="b">
         <v>0</v>
@@ -7075,11 +7104,6 @@
       <c r="AH50" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI50" t="inlineStr">
-        <is>
-          <t>Äldre bitvis flerskiktad granskog med inslag av tall, björk, sälg och gråal.</t>
         </is>
       </c>
       <c r="AJ50" t="inlineStr">
@@ -7117,37 +7141,38 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130887112</v>
+        <v>130887109</v>
       </c>
       <c r="B51" t="n">
-        <v>79245</v>
+        <v>97983</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -7155,10 +7180,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>495735</v>
+        <v>496004</v>
       </c>
       <c r="R51" t="n">
-        <v>7016071</v>
+        <v>7016371</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7193,11 +7218,6 @@
           <t>2026-01-26</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Enstaka bålar på gran.</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -7211,26 +7231,6 @@
       <c r="AH51" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>

--- a/artfynd/A 62696-2025 artfynd.xlsx
+++ b/artfynd/A 62696-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY51"/>
+  <dimension ref="A1:AZ51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -807,6 +812,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130887081</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -942,6 +952,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130887082</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1073,6 +1088,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130887112</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1199,6 +1219,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130887113</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1325,6 +1350,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130887114</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1451,6 +1481,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130887115</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1582,6 +1617,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130887116</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1713,6 +1753,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130887117</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1844,6 +1889,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130887118</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1975,6 +2025,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130887119</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2110,6 +2165,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130887120</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2236,6 +2296,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130887121</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2362,6 +2427,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130887122</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2488,6 +2558,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130887123</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2619,6 +2694,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130887124</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2745,6 +2825,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130887125</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2871,6 +2956,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130887126</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -3002,6 +3092,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130887127</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3133,6 +3228,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130887128</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3259,6 +3359,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130887129</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3390,6 +3495,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130887130</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3521,6 +3631,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130887131</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3652,6 +3767,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130887132</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3778,6 +3898,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130887133</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3917,6 +4042,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130887104</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -4047,6 +4177,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130887105</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -4182,6 +4317,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130887106</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4310,6 +4450,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130887107</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4449,6 +4594,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130887083</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4588,6 +4738,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130887084</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4723,6 +4878,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130887085</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4858,6 +5018,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130887086</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4993,6 +5158,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130887087</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -5132,6 +5302,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130887088</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -5267,6 +5442,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130887089</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5402,6 +5582,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130887090</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5537,6 +5722,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130887091</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5672,6 +5862,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130887092</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5807,6 +6002,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130887093</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5942,6 +6142,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130887094</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -6077,6 +6282,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130887095</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -6212,6 +6422,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130887096</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -6347,6 +6562,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130887097</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -6482,6 +6702,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130887098</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -6617,6 +6842,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130887099</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6752,6 +6982,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130887100</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6896,6 +7131,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130887101</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -7031,6 +7271,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130887102</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -7138,6 +7383,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130887108</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -7245,8 +7495,65 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130887109</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>